--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
   <si>
     <t>48957</t>
   </si>
@@ -67,12 +67,24 @@
     <t>435856</t>
   </si>
   <si>
+    <t>571915</t>
+  </si>
+  <si>
+    <t>571916</t>
+  </si>
+  <si>
     <t>435860</t>
   </si>
   <si>
     <t>435857</t>
   </si>
   <si>
+    <t>571917</t>
+  </si>
+  <si>
+    <t>571918</t>
+  </si>
+  <si>
     <t>435858</t>
   </si>
   <si>
@@ -109,12 +121,24 @@
     <t>Total de plazas de base ocupadas</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de plazas de base ocupadas por hombres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de plazas de base ocupadas por mujeres</t>
+  </si>
+  <si>
     <t>Total de plazas de base vacantes</t>
   </si>
   <si>
     <t>Total de plazas de confianza</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de plazas de confianza ocupadas por hombres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de plazas de confianza ocupadas por mujeres</t>
+  </si>
+  <si>
     <t>Total de plazas de confianza ocupadas</t>
   </si>
   <si>
@@ -133,7 +157,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>585</t>
@@ -148,25 +172,37 @@
     <t>Departamento de recursos humanos</t>
   </si>
   <si>
-    <t>C01C9CFD5430A1CC41E14AF682F9FBB0</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2022 al 30 de septiembre de 2022, la información reportada en este apartado es con base a la estructura orgánica vigente, aprobada y registrada por el órgano competente para Colegio de Bachilleres del Estado de Tlaxcala.</t>
+    <t>624C8CA4BFCBC4E2632B4EAF3886343F</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembere de 2023, la información reportada en este apartado es con base a la estructura orgánica vigente, aprobada y registrada por el órgano competente para Colegio de Bachilleres del Estado de Tlaxcala.</t>
   </si>
 </sst>
 </file>
@@ -559,31 +595,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="222.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="221.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -600,7 +638,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -615,7 +653,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -644,19 +682,31 @@
         <v>8</v>
       </c>
       <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" t="s">
+      <c r="Q4" t="s">
         <v>10</v>
       </c>
-      <c r="N4" t="s">
+      <c r="R4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -696,10 +746,22 @@
       <c r="N5" t="s">
         <v>24</v>
       </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -714,95 +776,123 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:R6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
